--- a/tame_output/ON/bt/strategyON_20240714.xlsx
+++ b/tame_output/ON/bt/strategyON_20240714.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-481.8%</t>
+          <t>-481.7%</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-126.3%</t>
+          <t>-126.2%</t>
         </is>
       </c>
     </row>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763532</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.201895457719575</v>
+        <v>-3.201375343768784</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.366395947953364</v>
+        <v>2.366603993533681</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.9771403553986477</v>
+        <v>0.9775586132018079</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.233794768594131</v>
+        <v>4.234045723276027</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240714.xlsx
+++ b/tame_output/ON/bt/strategyON_20240714.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.5%</t>
+          <t>-65.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-481.7%</t>
+          <t>-472.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-139.6%</t>
+          <t>-135.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-134.9%</t>
+          <t>-134.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-126.2%</t>
+          <t>-118.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.201375343768784</v>
+        <v>-3.108890116394614</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.366603993533681</v>
+        <v>2.403598084483349</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.9775586132018079</v>
+        <v>1.053516012600689</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.234045723276027</v>
+        <v>4.279620162915355</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240714.xlsx
+++ b/tame_output/ON/bt/strategyON_20240714.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.1%</t>
+          <t>-65.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-472.5%</t>
+          <t>-470.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-135.9%</t>
+          <t>-135.1%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-134.4%</t>
+          <t>-134.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -46976,10 +46976,10 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.869323839982079</v>
+        <v>-2.849292588161015</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.312441489385959</v>
+        <v>1.320453990114385</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7611042737070282</v>
@@ -46999,10 +46999,10 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.82495070834351</v>
+        <v>-2.804919456522446</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.330053609476822</v>
+        <v>1.338066110205248</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8054774053455968</v>
@@ -47022,10 +47022,10 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.702116487456343</v>
+        <v>-2.682085235635279</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.37358109197028</v>
+        <v>1.381593592698706</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8054774053455968</v>
@@ -47045,10 +47045,10 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.654460756895287</v>
+        <v>-2.634429505074223</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.399025141222507</v>
+        <v>1.407037641950933</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8531331359066524</v>
@@ -47068,10 +47068,10 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.553942598396532</v>
+        <v>-2.533911346575469</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.444124777996734</v>
+        <v>1.452137278725159</v>
       </c>
       <c r="F1979" t="n">
         <v>0.953651294405407</v>
@@ -47091,10 +47091,10 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.614609188798922</v>
+        <v>-2.594577936977858</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.40661281431165</v>
+        <v>1.414625315040076</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8719529776868733</v>
@@ -47114,10 +47114,10 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.569770787190524</v>
+        <v>-2.54973953536946</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.428645877565638</v>
+        <v>1.436658378294064</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8764964106317428</v>
@@ -47137,10 +47137,10 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.670529422947522</v>
+        <v>-2.650498171126458</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.392503362893917</v>
+        <v>1.400515863622342</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7876708419047374</v>
@@ -47160,10 +47160,10 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.626326585861622</v>
+        <v>-2.606295334040558</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.416064100256114</v>
+        <v>1.42407660098454</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8318736789906378</v>
@@ -47183,10 +47183,10 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.663305613525065</v>
+        <v>-2.643274361704001</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.399682489659984</v>
+        <v>1.40769499038841</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8688475807819683</v>
@@ -47206,10 +47206,10 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.505014195985793</v>
+        <v>-2.484982944164729</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.514246821858733</v>
+        <v>1.522259322587158</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8688475807819683</v>
@@ -47229,10 +47229,10 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.297372192351316</v>
+        <v>-2.277340940530252</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.595744327906776</v>
+        <v>1.603756828635202</v>
       </c>
       <c r="F1986" t="n">
         <v>1.076489584416445</v>
@@ -47252,10 +47252,10 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.246340099628788</v>
+        <v>-2.226308847807724</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.611105393234058</v>
+        <v>1.619117893962483</v>
       </c>
       <c r="F1987" t="n">
         <v>1.127521677138973</v>
@@ -47275,10 +47275,10 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.181115918501582</v>
+        <v>-2.161084666680519</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.654382469777645</v>
+        <v>1.662394970506071</v>
       </c>
       <c r="F1988" t="n">
         <v>1.192745858266178</v>
@@ -47298,10 +47298,10 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.143688898430449</v>
+        <v>-2.123657646609385</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.665314250105379</v>
+        <v>1.673326750833804</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19799739629536</v>
@@ -47321,10 +47321,10 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.163800554465157</v>
+        <v>-2.143769302644093</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.658526380022736</v>
+        <v>1.666538880751161</v>
       </c>
       <c r="F1990" t="n">
         <v>1.209024741292779</v>
@@ -47344,10 +47344,10 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.110055740037952</v>
+        <v>-2.090024488216888</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.840582076814828</v>
+        <v>1.848594577543254</v>
       </c>
       <c r="F1991" t="n">
         <v>1.219088050733241</v>
@@ -47367,10 +47367,10 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.03527347901294</v>
+        <v>-2.015242227191876</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.990607890442651</v>
+        <v>1.998620391171076</v>
       </c>
       <c r="F1992" t="n">
         <v>1.293870311758254</v>
@@ -47390,10 +47390,10 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.009189394749132</v>
+        <v>-1.989158142928068</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.992749500162033</v>
+        <v>2.000762000890458</v>
       </c>
       <c r="F1993" t="n">
         <v>1.293870311758254</v>
@@ -47413,10 +47413,10 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.931058213900185</v>
+        <v>-1.911026962079121</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.022195168085391</v>
+        <v>2.030207668813817</v>
       </c>
       <c r="F1994" t="n">
         <v>1.368047122641939</v>
@@ -47436,10 +47436,10 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.922165752506902</v>
+        <v>-1.902134500685838</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.043306558369496</v>
+        <v>2.051319059097921</v>
       </c>
       <c r="F1995" t="n">
         <v>1.368047122641939</v>
@@ -47459,10 +47459,10 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.09064186947678</v>
+        <v>-2.070610617655716</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.967771158986129</v>
+        <v>1.975783659714554</v>
       </c>
       <c r="F1996" t="n">
         <v>1.340099286925358</v>
@@ -47482,10 +47482,10 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.392842340615196</v>
+        <v>-1.372811088794132</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.228160667718623</v>
+        <v>2.236173168447049</v>
       </c>
       <c r="F1997" t="n">
         <v>1.269751227554947</v>
@@ -47505,10 +47505,10 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.370121236932044</v>
+        <v>-1.35008998511098</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.227913131688789</v>
+        <v>2.235925632417215</v>
       </c>
       <c r="F1998" t="n">
         <v>1.269751227554947</v>
@@ -47528,10 +47528,10 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.368396193642</v>
+        <v>-1.348364941820936</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.387509274855976</v>
+        <v>2.395521775584401</v>
       </c>
       <c r="F1999" t="n">
         <v>1.271476270844991</v>
@@ -47551,10 +47551,10 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.523177200420256</v>
+        <v>-1.503145948599192</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.36267469463832</v>
+        <v>2.370687195366746</v>
       </c>
       <c r="F2000" t="n">
         <v>1.238108596790515</v>
@@ -47574,10 +47574,10 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.471741867035596</v>
+        <v>-1.451710615214532</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.379924183981729</v>
+        <v>2.387936684710155</v>
       </c>
       <c r="F2001" t="n">
         <v>1.289543930175174</v>
@@ -47597,10 +47597,10 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.444790642709108</v>
+        <v>-1.424759390888044</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.400710827357066</v>
+        <v>2.408723328085491</v>
       </c>
       <c r="F2002" t="n">
         <v>1.304424276202893</v>
@@ -47620,10 +47620,10 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.580743650765424</v>
+        <v>-1.56071239894436</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.530432756279499</v>
+        <v>2.538445257007925</v>
       </c>
       <c r="F2003" t="n">
         <v>1.304424276202893</v>
@@ -47643,10 +47643,10 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.603151768570296</v>
+        <v>-1.583120516749232</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.513586204060544</v>
+        <v>2.521598704788969</v>
       </c>
       <c r="F2004" t="n">
         <v>1.304424276202893</v>
@@ -47666,10 +47666,10 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.751157536049695</v>
+        <v>-1.731126284228631</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.456437896618421</v>
+        <v>2.464450397346847</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217697267339352</v>
@@ -47689,10 +47689,10 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.760598461938225</v>
+        <v>-1.740567210117161</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.508915243984856</v>
+        <v>2.516927744713282</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340124384882743</v>
@@ -47712,10 +47712,10 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.759311698398669</v>
+        <v>-1.739280446577605</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.51232104394598</v>
+        <v>2.520333544674406</v>
       </c>
       <c r="F2007" t="n">
         <v>1.3414111484223</v>
@@ -47735,10 +47735,10 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.76086875238796</v>
+        <v>-1.740837500566896</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.509810035244039</v>
+        <v>2.517822535972464</v>
       </c>
       <c r="F2008" t="n">
         <v>1.3414111484223</v>
@@ -47758,10 +47758,10 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.768140637911425</v>
+        <v>-1.748109386090361</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.501721510637515</v>
+        <v>2.509734011365941</v>
       </c>
       <c r="F2009" t="n">
         <v>1.334139262898835</v>
@@ -47781,10 +47781,10 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.766299618853173</v>
+        <v>-1.746268367032109</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.500891928470968</v>
+        <v>2.508904429199394</v>
       </c>
       <c r="F2010" t="n">
         <v>1.335407489570303</v>
@@ -47804,10 +47804,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.773208324352854</v>
+        <v>-1.75317707253179</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.511201853137014</v>
+        <v>2.51921435386544</v>
       </c>
       <c r="F2011" t="n">
         <v>1.335407489570303</v>
@@ -47827,10 +47827,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.774769967167714</v>
+        <v>-1.75473871534665</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.510577196011071</v>
+        <v>2.518589696739496</v>
       </c>
       <c r="F2012" t="n">
         <v>1.335407489570303</v>
@@ -47850,10 +47850,10 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.802670754277186</v>
+        <v>-1.782639502456123</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.497940922294283</v>
+        <v>2.505953423022709</v>
       </c>
       <c r="F2013" t="n">
         <v>1.300810565427369</v>
@@ -47873,10 +47873,10 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.80570375178986</v>
+        <v>-1.785672499968797</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.493492167266413</v>
+        <v>2.501504667994838</v>
       </c>
       <c r="F2014" t="n">
         <v>1.297777567914695</v>
@@ -47896,10 +47896,10 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.825765073066367</v>
+        <v>-1.805733821245304</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.552173598346313</v>
+        <v>2.560186099074739</v>
       </c>
       <c r="F2015" t="n">
         <v>1.277716246638188</v>
@@ -47919,10 +47919,10 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.082485891061191</v>
+        <v>-2.062454639240127</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.589796990150231</v>
+        <v>2.597809490878657</v>
       </c>
       <c r="F2016" t="n">
         <v>1.169301672494373</v>
@@ -47942,10 +47942,10 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.236472308837332</v>
+        <v>-2.216441057016268</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.597182692185414</v>
+        <v>2.60519519291384</v>
       </c>
       <c r="F2017" t="n">
         <v>1.169301672494373</v>
@@ -47965,10 +47965,10 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.185950405009666</v>
+        <v>-2.165919153188602</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.603442655836602</v>
+        <v>2.611455156565027</v>
       </c>
       <c r="F2018" t="n">
         <v>1.169301672494373</v>
@@ -47988,10 +47988,10 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.43842555901739</v>
+        <v>-2.418394307196326</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.514323083288926</v>
+        <v>2.522335584017351</v>
       </c>
       <c r="F2019" t="n">
         <v>1.169301672494373</v>
@@ -48011,10 +48011,10 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.707898360939098</v>
+        <v>-2.687867109118034</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.407744497039186</v>
+        <v>2.415756997767612</v>
       </c>
       <c r="F2020" t="n">
         <v>1.169301672494373</v>
@@ -48034,10 +48034,10 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.865442432668539</v>
+        <v>-2.845411180847476</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.348848610574731</v>
+        <v>2.356861111303157</v>
       </c>
       <c r="F2021" t="n">
         <v>1.102399867354098</v>
@@ -48057,10 +48057,10 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-2.994292983370586</v>
+        <v>-2.974261731549522</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.292386243030102</v>
+        <v>2.300398743758528</v>
       </c>
       <c r="F2022" t="n">
         <v>1.061406458503377</v>
@@ -48080,10 +48080,10 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.111260676009477</v>
+        <v>-3.091229424188413</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.40780322267359</v>
+        <v>2.415815723402015</v>
       </c>
       <c r="F2023" t="n">
         <v>1.061406458503377</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.853675259895444</v>
+        <v>3.791828302411098</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.108890116394614</v>
+        <v>-3.08885886457355</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.403598084483349</v>
+        <v>2.411610585211775</v>
       </c>
       <c r="F2024" t="n">
         <v>1.053516012600689</v>

--- a/tame_output/ON/bt/strategyON_20240714.xlsx
+++ b/tame_output/ON/bt/strategyON_20240714.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,16 +926,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.0%</t>
+          <t>-65.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-470.5%</t>
+          <t>-480.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-135.1%</t>
+          <t>-138.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-134.5%</t>
+          <t>-135.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-118.6%</t>
+          <t>-126.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-77.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2024"/>
+  <dimension ref="A1:G2025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46976,10 +46976,10 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.849292588161015</v>
+        <v>-2.85761417188824</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.320453990114385</v>
+        <v>1.317125356623494</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7611042737070282</v>
@@ -46999,10 +46999,10 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.804919456522446</v>
+        <v>-2.813241040249672</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.338066110205248</v>
+        <v>1.334737476714358</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8054774053455968</v>
@@ -47022,10 +47022,10 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.682085235635279</v>
+        <v>-2.690406819362504</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.381593592698706</v>
+        <v>1.378264959207816</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8054774053455968</v>
@@ -47045,10 +47045,10 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.634429505074223</v>
+        <v>-2.642751088801448</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.407037641950933</v>
+        <v>1.403709008460043</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8531331359066524</v>
@@ -47068,10 +47068,10 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.533911346575469</v>
+        <v>-2.542232930302694</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.452137278725159</v>
+        <v>1.448808645234269</v>
       </c>
       <c r="F1979" t="n">
         <v>0.953651294405407</v>
@@ -47091,10 +47091,10 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.594577936977858</v>
+        <v>-2.602899520705083</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.414625315040076</v>
+        <v>1.411296681549186</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8719529776868733</v>
@@ -47114,10 +47114,10 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.54973953536946</v>
+        <v>-2.558061119096685</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.436658378294064</v>
+        <v>1.433329744803174</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8764964106317428</v>
@@ -47137,10 +47137,10 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.650498171126458</v>
+        <v>-2.658819754853683</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.400515863622342</v>
+        <v>1.397187230131452</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7876708419047374</v>
@@ -47160,10 +47160,10 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.606295334040558</v>
+        <v>-2.614616917767783</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.42407660098454</v>
+        <v>1.420747967493649</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8318736789906378</v>
@@ -47183,10 +47183,10 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.643274361704001</v>
+        <v>-2.651595945431226</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.40769499038841</v>
+        <v>1.40436635689752</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8688475807819683</v>
@@ -47206,10 +47206,10 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.484982944164729</v>
+        <v>-2.493304527891954</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.522259322587158</v>
+        <v>1.518930689096268</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8688475807819683</v>
@@ -47229,10 +47229,10 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.277340940530252</v>
+        <v>-2.285662524257478</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.603756828635202</v>
+        <v>1.600428195144312</v>
       </c>
       <c r="F1986" t="n">
         <v>1.076489584416445</v>
@@ -47252,10 +47252,10 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.226308847807724</v>
+        <v>-2.23463043153495</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.619117893962483</v>
+        <v>1.615789260471593</v>
       </c>
       <c r="F1987" t="n">
         <v>1.127521677138973</v>
@@ -47275,10 +47275,10 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.161084666680519</v>
+        <v>-2.169406250407744</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.662394970506071</v>
+        <v>1.65906633701518</v>
       </c>
       <c r="F1988" t="n">
         <v>1.192745858266178</v>
@@ -47298,10 +47298,10 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.123657646609385</v>
+        <v>-2.13197923033661</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.673326750833804</v>
+        <v>1.669998117342914</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19799739629536</v>
@@ -47321,10 +47321,10 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.143769302644093</v>
+        <v>-2.152090886371318</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.666538880751161</v>
+        <v>1.663210247260271</v>
       </c>
       <c r="F1990" t="n">
         <v>1.209024741292779</v>
@@ -47344,10 +47344,10 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.090024488216888</v>
+        <v>-2.098346071944114</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.848594577543254</v>
+        <v>1.845265944052364</v>
       </c>
       <c r="F1991" t="n">
         <v>1.219088050733241</v>
@@ -47367,10 +47367,10 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.015242227191876</v>
+        <v>-2.023563810919101</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.998620391171076</v>
+        <v>1.995291757680186</v>
       </c>
       <c r="F1992" t="n">
         <v>1.293870311758254</v>
@@ -47390,10 +47390,10 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-1.989158142928068</v>
+        <v>-1.997479726655293</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.000762000890458</v>
+        <v>1.997433367399569</v>
       </c>
       <c r="F1993" t="n">
         <v>1.293870311758254</v>
@@ -47413,10 +47413,10 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.911026962079121</v>
+        <v>-1.919348545806346</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.030207668813817</v>
+        <v>2.026879035322926</v>
       </c>
       <c r="F1994" t="n">
         <v>1.368047122641939</v>
@@ -47436,10 +47436,10 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.902134500685838</v>
+        <v>-1.910456084413063</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.051319059097921</v>
+        <v>2.047990425607031</v>
       </c>
       <c r="F1995" t="n">
         <v>1.368047122641939</v>
@@ -47459,10 +47459,10 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.070610617655716</v>
+        <v>-2.078932201382941</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.975783659714554</v>
+        <v>1.972455026223664</v>
       </c>
       <c r="F1996" t="n">
         <v>1.340099286925358</v>
@@ -47482,10 +47482,10 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.372811088794132</v>
+        <v>-1.381132672521358</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.236173168447049</v>
+        <v>2.232844534956159</v>
       </c>
       <c r="F1997" t="n">
         <v>1.269751227554947</v>
@@ -47505,10 +47505,10 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.35008998511098</v>
+        <v>-1.358411568838205</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.235925632417215</v>
+        <v>2.232596998926325</v>
       </c>
       <c r="F1998" t="n">
         <v>1.269751227554947</v>
@@ -47528,10 +47528,10 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.348364941820936</v>
+        <v>-1.356686525548161</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.395521775584401</v>
+        <v>2.392193142093511</v>
       </c>
       <c r="F1999" t="n">
         <v>1.271476270844991</v>
@@ -47551,10 +47551,10 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.503145948599192</v>
+        <v>-1.511467532326417</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.370687195366746</v>
+        <v>2.367358561875855</v>
       </c>
       <c r="F2000" t="n">
         <v>1.238108596790515</v>
@@ -47574,10 +47574,10 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.451710615214532</v>
+        <v>-1.460032198941757</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.387936684710155</v>
+        <v>2.384608051219264</v>
       </c>
       <c r="F2001" t="n">
         <v>1.289543930175174</v>
@@ -47597,10 +47597,10 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.424759390888044</v>
+        <v>-1.433080974615269</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.408723328085491</v>
+        <v>2.405394694594601</v>
       </c>
       <c r="F2002" t="n">
         <v>1.304424276202893</v>
@@ -47620,10 +47620,10 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.56071239894436</v>
+        <v>-1.569033982671585</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.538445257007925</v>
+        <v>2.535116623517035</v>
       </c>
       <c r="F2003" t="n">
         <v>1.304424276202893</v>
@@ -47643,10 +47643,10 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.583120516749232</v>
+        <v>-1.591442100476457</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.521598704788969</v>
+        <v>2.518270071298079</v>
       </c>
       <c r="F2004" t="n">
         <v>1.304424276202893</v>
@@ -47666,10 +47666,10 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.731126284228631</v>
+        <v>-1.739447867955857</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.464450397346847</v>
+        <v>2.461121763855957</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217697267339352</v>
@@ -47689,10 +47689,10 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.740567210117161</v>
+        <v>-1.748888793844386</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.516927744713282</v>
+        <v>2.513599111222392</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340124384882743</v>
@@ -47712,10 +47712,10 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.739280446577605</v>
+        <v>-1.74760203030483</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.520333544674406</v>
+        <v>2.517004911183515</v>
       </c>
       <c r="F2007" t="n">
         <v>1.3414111484223</v>
@@ -47735,10 +47735,10 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.740837500566896</v>
+        <v>-1.749159084294121</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.517822535972464</v>
+        <v>2.514493902481574</v>
       </c>
       <c r="F2008" t="n">
         <v>1.3414111484223</v>
@@ -47758,10 +47758,10 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.748109386090361</v>
+        <v>-1.756430969817586</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.509734011365941</v>
+        <v>2.50640537787505</v>
       </c>
       <c r="F2009" t="n">
         <v>1.334139262898835</v>
@@ -47781,10 +47781,10 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.746268367032109</v>
+        <v>-1.754589950759335</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.508904429199394</v>
+        <v>2.505575795708503</v>
       </c>
       <c r="F2010" t="n">
         <v>1.335407489570303</v>
@@ -47804,10 +47804,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.75317707253179</v>
+        <v>-1.761498656259015</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.51921435386544</v>
+        <v>2.51588572037455</v>
       </c>
       <c r="F2011" t="n">
         <v>1.335407489570303</v>
@@ -47827,10 +47827,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.75473871534665</v>
+        <v>-1.763060299073875</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.518589696739496</v>
+        <v>2.515261063248606</v>
       </c>
       <c r="F2012" t="n">
         <v>1.335407489570303</v>
@@ -47850,10 +47850,10 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.782639502456123</v>
+        <v>-1.790961086183348</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.505953423022709</v>
+        <v>2.502624789531819</v>
       </c>
       <c r="F2013" t="n">
         <v>1.300810565427369</v>
@@ -47873,10 +47873,10 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.785672499968797</v>
+        <v>-1.793994083696022</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.501504667994838</v>
+        <v>2.498176034503948</v>
       </c>
       <c r="F2014" t="n">
         <v>1.297777567914695</v>
@@ -47896,10 +47896,10 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.805733821245304</v>
+        <v>-1.814055404972529</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.560186099074739</v>
+        <v>2.556857465583849</v>
       </c>
       <c r="F2015" t="n">
         <v>1.277716246638188</v>
@@ -47919,10 +47919,10 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.062454639240127</v>
+        <v>-2.070776222967353</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.597809490878657</v>
+        <v>2.594480857387766</v>
       </c>
       <c r="F2016" t="n">
         <v>1.169301672494373</v>
@@ -47942,10 +47942,10 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.216441057016268</v>
+        <v>-2.224762640743493</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.60519519291384</v>
+        <v>2.60186655942295</v>
       </c>
       <c r="F2017" t="n">
         <v>1.169301672494373</v>
@@ -47965,10 +47965,10 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.165919153188602</v>
+        <v>-2.174240736915827</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.611455156565027</v>
+        <v>2.608126523074137</v>
       </c>
       <c r="F2018" t="n">
         <v>1.169301672494373</v>
@@ -47988,10 +47988,10 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.418394307196326</v>
+        <v>-2.426715890923552</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.522335584017351</v>
+        <v>2.519006950526461</v>
       </c>
       <c r="F2019" t="n">
         <v>1.169301672494373</v>
@@ -48011,10 +48011,10 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.687867109118034</v>
+        <v>-2.69618869284526</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.415756997767612</v>
+        <v>2.412428364276722</v>
       </c>
       <c r="F2020" t="n">
         <v>1.169301672494373</v>
@@ -48034,10 +48034,10 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.845411180847476</v>
+        <v>-2.853732764574701</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.356861111303157</v>
+        <v>2.353532477812267</v>
       </c>
       <c r="F2021" t="n">
         <v>1.102399867354098</v>
@@ -48057,10 +48057,10 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-2.974261731549522</v>
+        <v>-2.982583315276747</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.300398743758528</v>
+        <v>2.297070110267637</v>
       </c>
       <c r="F2022" t="n">
         <v>1.061406458503377</v>
@@ -48080,10 +48080,10 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.091229424188413</v>
+        <v>-3.099551007915638</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.415815723402015</v>
+        <v>2.412487089911125</v>
       </c>
       <c r="F2023" t="n">
         <v>1.061406458503377</v>
@@ -48097,22 +48097,45 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.791828302411098</v>
+        <v>3.696553628456693</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.08885886457355</v>
+        <v>-3.184268950136592</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.411610585211775</v>
+        <v>2.373446550986558</v>
       </c>
       <c r="F2024" t="n">
-        <v>1.053516012600689</v>
+        <v>0.9762904295753305</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.279620162915355</v>
+        <v>4.23328481310014</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="2" t="n">
+        <v>45487</v>
+      </c>
+      <c r="B2025" t="n">
+        <v>3.789181267436577</v>
+      </c>
+      <c r="C2025" t="n">
+        <v>3.691582213266134</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>-3.184268950136592</v>
+      </c>
+      <c r="E2025" t="n">
+        <v>2.373446550986558</v>
+      </c>
+      <c r="F2025" t="n">
+        <v>0.9762904295753305</v>
+      </c>
+      <c r="G2025" t="n">
+        <v>3.684646010252501</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240714.xlsx
+++ b/tame_output/ON/bt/strategyON_20240714.xlsx
@@ -48123,7 +48123,7 @@
         <v>3.789181267436577</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.691582213266134</v>
+        <v>3.691582213266133</v>
       </c>
       <c r="D2025" t="n">
         <v>-3.184268950136592</v>

--- a/tame_output/ON/bt/strategyON_20240714.xlsx
+++ b/tame_output/ON/bt/strategyON_20240714.xlsx
@@ -48123,7 +48123,7 @@
         <v>3.789181267436577</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.691582213266133</v>
+        <v>3.691582213266134</v>
       </c>
       <c r="D2025" t="n">
         <v>-3.184268950136592</v>

--- a/tame_output/ON/bt/strategyON_20240714.xlsx
+++ b/tame_output/ON/bt/strategyON_20240714.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>43.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>121.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.6%</t>
+          <t>-65.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.9%</t>
+          <t>457.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-480.0%</t>
+          <t>-479.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-138.9%</t>
+          <t>-137.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.0%</t>
+          <t>-135.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-126.4%</t>
+          <t>-137.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-28.4%</t>
         </is>
       </c>
     </row>
@@ -47390,10 +47390,10 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-1.997479726655293</v>
+        <v>-1.989825504854874</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.997433367399569</v>
+        <v>2.000495056119736</v>
       </c>
       <c r="F1993" t="n">
         <v>1.293870311758254</v>
@@ -47413,10 +47413,10 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.919348545806346</v>
+        <v>-1.911694324005927</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.026879035322926</v>
+        <v>2.029940724043094</v>
       </c>
       <c r="F1994" t="n">
         <v>1.368047122641939</v>
@@ -47436,10 +47436,10 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.910456084413063</v>
+        <v>-1.902801862612644</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.047990425607031</v>
+        <v>2.051052114327199</v>
       </c>
       <c r="F1995" t="n">
         <v>1.368047122641939</v>
@@ -47459,10 +47459,10 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.078932201382941</v>
+        <v>-2.071277979582522</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.972455026223664</v>
+        <v>1.975516714943832</v>
       </c>
       <c r="F1996" t="n">
         <v>1.340099286925358</v>
@@ -47482,10 +47482,10 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.381132672521358</v>
+        <v>-1.373478450720939</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.232844534956159</v>
+        <v>2.235906223676327</v>
       </c>
       <c r="F1997" t="n">
         <v>1.269751227554947</v>
@@ -47505,10 +47505,10 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.358411568838205</v>
+        <v>-1.350757347037786</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.232596998926325</v>
+        <v>2.235658687646492</v>
       </c>
       <c r="F1998" t="n">
         <v>1.269751227554947</v>
@@ -47528,10 +47528,10 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.356686525548161</v>
+        <v>-1.349032303747743</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.392193142093511</v>
+        <v>2.395254830813679</v>
       </c>
       <c r="F1999" t="n">
         <v>1.271476270844991</v>
@@ -47551,10 +47551,10 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.511467532326417</v>
+        <v>-1.503813310525998</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.367358561875855</v>
+        <v>2.370420250596023</v>
       </c>
       <c r="F2000" t="n">
         <v>1.238108596790515</v>
@@ -47574,16 +47574,16 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.460032198941757</v>
+        <v>-1.490568365546765</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.384608051219264</v>
+        <v>2.372393584577261</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.289543930175174</v>
+        <v>1.251353541769748</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.742703713214819</v>
+        <v>3.719789480171563</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.433080974615269</v>
+        <v>-1.463617141220277</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.405394694594601</v>
+        <v>2.393180227952598</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.304424276202893</v>
+        <v>1.266233887797467</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.761638074476193</v>
+        <v>3.738723841432936</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.569033982671585</v>
+        <v>-1.599570149276593</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.535116623517035</v>
+        <v>2.522902156875031</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.304424276202893</v>
+        <v>1.266233887797467</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.945741206621152</v>
+        <v>3.922826973577896</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.591442100476457</v>
+        <v>-1.621978267081465</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.518270071298079</v>
+        <v>2.506055604656076</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.304424276202893</v>
+        <v>1.266233887797467</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.937857901524145</v>
+        <v>3.914943668480889</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.739447867955857</v>
+        <v>-1.769984034560864</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.461121763855957</v>
+        <v>2.448907297213954</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.217697267339352</v>
+        <v>1.179506878933925</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.887875695755658</v>
+        <v>3.864961462712402</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.748888793844386</v>
+        <v>-1.779424960449394</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.513599111222392</v>
+        <v>2.501384644580389</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.340124384882743</v>
+        <v>1.301933996477317</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.01758568400354</v>
+        <v>3.994671450960284</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.74760203030483</v>
+        <v>-1.778138196909838</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.517004911183515</v>
+        <v>2.504790444541512</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.3414111484223</v>
+        <v>1.303220760016873</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.021248836672575</v>
+        <v>3.998334603629319</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.749159084294121</v>
+        <v>-1.779695250899129</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.514493902481574</v>
+        <v>2.502279435839571</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.3414111484223</v>
+        <v>1.303220760016873</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.01936064956635</v>
+        <v>3.996446416523094</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.756430969817586</v>
+        <v>-1.786967136422594</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.50640537787505</v>
+        <v>2.494190911233047</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.334139262898835</v>
+        <v>1.295948874493408</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.009817747855133</v>
+        <v>3.986903514811877</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.754589950759335</v>
+        <v>-1.785126117364342</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.505575795708503</v>
+        <v>2.4933613290665</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.335407489570303</v>
+        <v>1.297217101164877</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.009012694068167</v>
+        <v>3.986098461024911</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.761498656259015</v>
+        <v>-1.792034822864023</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.51588572037455</v>
+        <v>2.503671253732547</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.335407489570303</v>
+        <v>1.297217101164877</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.022086100934086</v>
+        <v>3.999171867890829</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.763060299073875</v>
+        <v>-1.793596465678883</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.515261063248606</v>
+        <v>2.503046596606603</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.335407489570303</v>
+        <v>1.297217101164877</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.022086100934086</v>
+        <v>3.999171867890829</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.790961086183348</v>
+        <v>-1.821497252788356</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.502624789531819</v>
+        <v>2.490410322889816</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.300810565427369</v>
+        <v>1.262620177021942</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.999851987575327</v>
+        <v>3.97693775453207</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.793994083696022</v>
+        <v>-1.824530250301029</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.498176034503948</v>
+        <v>2.485961567861945</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.297777567914695</v>
+        <v>1.259587179509268</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.99479663304492</v>
+        <v>3.971882400001665</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.814055404972529</v>
+        <v>-1.844591571577537</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.556857465583849</v>
+        <v>2.544642998941846</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.277716246638188</v>
+        <v>1.239525858232761</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.04946579986952</v>
+        <v>4.026551566826265</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.070776222967353</v>
+        <v>-2.10131238957236</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.594480857387766</v>
+        <v>2.582266390745763</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.169301672494373</v>
+        <v>1.131111284088946</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.124728774385079</v>
+        <v>4.101814541341823</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.224762640743493</v>
+        <v>-2.255298807348501</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.60186655942295</v>
+        <v>2.589652092780947</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.169301672494373</v>
+        <v>1.131111284088946</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.193709043530719</v>
+        <v>4.170794810487463</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.174240736915827</v>
+        <v>-2.204776903520835</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.608126523074137</v>
+        <v>2.595912056432134</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.169301672494373</v>
+        <v>1.131111284088946</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.179760245650839</v>
+        <v>4.156846012607583</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.426715890923552</v>
+        <v>-2.457252057528559</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.519006950526461</v>
+        <v>2.506792483884458</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.169301672494373</v>
+        <v>1.131111284088946</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.191630734706253</v>
+        <v>4.168716501662997</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.69618869284526</v>
+        <v>-2.726724859450267</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.412428364276722</v>
+        <v>2.400213897634718</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.169301672494373</v>
+        <v>1.131111284088946</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.192841269225197</v>
+        <v>4.169927036181941</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.853732764574701</v>
+        <v>-2.884268931179709</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.353532477812267</v>
+        <v>2.341318011170264</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.102399867354098</v>
+        <v>1.064209478948672</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.156821928368354</v>
+        <v>4.133907695325098</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-2.982583315276747</v>
+        <v>-3.013119481881755</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.297070110267637</v>
+        <v>2.284855643625634</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.061406458503377</v>
+        <v>1.02321607009795</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.12730373579411</v>
+        <v>4.104389502750855</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.099551007915638</v>
+        <v>-3.130087174520646</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.412487089911125</v>
+        <v>2.400272623269122</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.061406458503377</v>
+        <v>1.02321607009795</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.289507792493154</v>
+        <v>4.266593559449898</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456693</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.184268950136592</v>
+        <v>-3.231465774675497</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.373446550986558</v>
+        <v>2.354567821170996</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.9762904295753305</v>
+        <v>0.8643296411954772</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.23328481310014</v>
+        <v>4.166108340072229</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.789181267436577</v>
+        <v>3.710463051900209</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.691582213266134</v>
+        <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.184268950136592</v>
+        <v>-3.176388224128809</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.373446550986558</v>
+        <v>2.386828258958162</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.9762904295753305</v>
+        <v>0.8643296411954772</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.684646010252501</v>
+        <v>4.17633775764072</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240714.xlsx
+++ b/tame_output/ON/bt/strategyON_20240714.xlsx
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.7%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.7%</t>
+          <t>457.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-479.2%</t>
+          <t>-480.0%</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-137.5%</t>
+          <t>-137.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.8%</t>
+          <t>-135.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-137.6%</t>
+          <t>-130.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-24.3%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.85761417188824</v>
+        <v>-2.869323839982079</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.317125356623494</v>
+        <v>1.312441489385959</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7611042737070282</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.813241040249672</v>
+        <v>-2.82495070834351</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.334737476714358</v>
+        <v>1.330053609476822</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8054774053455968</v>
@@ -47022,10 +47022,10 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.690406819362504</v>
+        <v>-2.702116487456343</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.378264959207816</v>
+        <v>1.37358109197028</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8054774053455968</v>
@@ -47045,10 +47045,10 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.642751088801448</v>
+        <v>-2.654460756895287</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.403709008460043</v>
+        <v>1.399025141222507</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8531331359066524</v>
@@ -47068,10 +47068,10 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.542232930302694</v>
+        <v>-2.553942598396532</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.448808645234269</v>
+        <v>1.444124777996734</v>
       </c>
       <c r="F1979" t="n">
         <v>0.953651294405407</v>
@@ -47091,10 +47091,10 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.602899520705083</v>
+        <v>-2.614609188798922</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.411296681549186</v>
+        <v>1.40661281431165</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8719529776868733</v>
@@ -47114,10 +47114,10 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.558061119096685</v>
+        <v>-2.569770787190524</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.433329744803174</v>
+        <v>1.428645877565638</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8764964106317428</v>
@@ -47137,10 +47137,10 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.658819754853683</v>
+        <v>-2.670529422947522</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.397187230131452</v>
+        <v>1.392503362893917</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7876708419047374</v>
@@ -47160,10 +47160,10 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.614616917767783</v>
+        <v>-2.626326585861622</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.420747967493649</v>
+        <v>1.416064100256114</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8318736789906378</v>
@@ -47183,10 +47183,10 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.651595945431226</v>
+        <v>-2.663305613525065</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.40436635689752</v>
+        <v>1.399682489659984</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8688475807819683</v>
@@ -47206,10 +47206,10 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.493304527891954</v>
+        <v>-2.505014195985793</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.518930689096268</v>
+        <v>1.514246821858733</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8688475807819683</v>
@@ -47229,10 +47229,10 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.285662524257478</v>
+        <v>-2.297372192351316</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.600428195144312</v>
+        <v>1.595744327906776</v>
       </c>
       <c r="F1986" t="n">
         <v>1.076489584416445</v>
@@ -47252,10 +47252,10 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.23463043153495</v>
+        <v>-2.246340099628788</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.615789260471593</v>
+        <v>1.611105393234058</v>
       </c>
       <c r="F1987" t="n">
         <v>1.127521677138973</v>
@@ -47275,10 +47275,10 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.169406250407744</v>
+        <v>-2.181115918501582</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.65906633701518</v>
+        <v>1.654382469777645</v>
       </c>
       <c r="F1988" t="n">
         <v>1.192745858266178</v>
@@ -47298,10 +47298,10 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.13197923033661</v>
+        <v>-2.143688898430449</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.669998117342914</v>
+        <v>1.665314250105379</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19799739629536</v>
@@ -47321,10 +47321,10 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.152090886371318</v>
+        <v>-2.163800554465157</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.663210247260271</v>
+        <v>1.658526380022736</v>
       </c>
       <c r="F1990" t="n">
         <v>1.209024741292779</v>
@@ -47344,10 +47344,10 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.098346071944114</v>
+        <v>-2.110055740037952</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.845265944052364</v>
+        <v>1.840582076814828</v>
       </c>
       <c r="F1991" t="n">
         <v>1.219088050733241</v>
@@ -47367,10 +47367,10 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.023563810919101</v>
+        <v>-2.03527347901294</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.995291757680186</v>
+        <v>1.990607890442651</v>
       </c>
       <c r="F1992" t="n">
         <v>1.293870311758254</v>
@@ -47390,10 +47390,10 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-1.989825504854874</v>
+        <v>-2.009189394749132</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.000495056119736</v>
+        <v>1.992749500162033</v>
       </c>
       <c r="F1993" t="n">
         <v>1.293870311758254</v>
@@ -47413,10 +47413,10 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.911694324005927</v>
+        <v>-1.931058213900185</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.029940724043094</v>
+        <v>2.022195168085391</v>
       </c>
       <c r="F1994" t="n">
         <v>1.368047122641939</v>
@@ -47436,10 +47436,10 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.902801862612644</v>
+        <v>-1.922165752506902</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.051052114327199</v>
+        <v>2.043306558369496</v>
       </c>
       <c r="F1995" t="n">
         <v>1.368047122641939</v>
@@ -47459,10 +47459,10 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.071277979582522</v>
+        <v>-2.09064186947678</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.975516714943832</v>
+        <v>1.967771158986129</v>
       </c>
       <c r="F1996" t="n">
         <v>1.340099286925358</v>
@@ -47482,10 +47482,10 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.373478450720939</v>
+        <v>-1.392842340615196</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.235906223676327</v>
+        <v>2.228160667718623</v>
       </c>
       <c r="F1997" t="n">
         <v>1.269751227554947</v>
@@ -47505,10 +47505,10 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.350757347037786</v>
+        <v>-1.370121236932044</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.235658687646492</v>
+        <v>2.227913131688789</v>
       </c>
       <c r="F1998" t="n">
         <v>1.269751227554947</v>
@@ -47528,10 +47528,10 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.349032303747743</v>
+        <v>-1.368396193642</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.395254830813679</v>
+        <v>2.387509274855976</v>
       </c>
       <c r="F1999" t="n">
         <v>1.271476270844991</v>
@@ -47551,10 +47551,10 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.503813310525998</v>
+        <v>-1.523177200420256</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.370420250596023</v>
+        <v>2.36267469463832</v>
       </c>
       <c r="F2000" t="n">
         <v>1.238108596790515</v>
@@ -47574,16 +47574,16 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.490568365546765</v>
+        <v>-1.516122510205082</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.372393584577261</v>
+        <v>2.362171926713935</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.251353541769748</v>
+        <v>1.245163287005689</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.719789480171563</v>
+        <v>3.716075327313128</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.463617141220277</v>
+        <v>-1.489171285878594</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.393180227952598</v>
+        <v>2.382958570089272</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.266233887797467</v>
+        <v>1.260043633033408</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.738723841432936</v>
+        <v>3.735009688574501</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.599570149276593</v>
+        <v>-1.62512429393491</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.522902156875031</v>
+        <v>2.512680499011705</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.266233887797467</v>
+        <v>1.260043633033408</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.922826973577896</v>
+        <v>3.919112820719461</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.621978267081465</v>
+        <v>-1.647532411739782</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.506055604656076</v>
+        <v>2.495833946792749</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.266233887797467</v>
+        <v>1.260043633033408</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.914943668480889</v>
+        <v>3.911229515622454</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.769984034560864</v>
+        <v>-1.795538179219181</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.448907297213954</v>
+        <v>2.438685639350627</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.179506878933925</v>
+        <v>1.173316624169866</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.864961462712402</v>
+        <v>3.861247309853967</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.779424960449394</v>
+        <v>-1.804979105107711</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.501384644580389</v>
+        <v>2.491162986717062</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.301933996477317</v>
+        <v>1.295743741713258</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.994671450960284</v>
+        <v>3.990957298101849</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.778138196909838</v>
+        <v>-1.803692341568154</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.504790444541512</v>
+        <v>2.494568786678186</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.303220760016873</v>
+        <v>1.297030505252814</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.998334603629319</v>
+        <v>3.994620450770883</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.779695250899129</v>
+        <v>-1.805249395557446</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.502279435839571</v>
+        <v>2.492057777976244</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.303220760016873</v>
+        <v>1.297030505252814</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.996446416523094</v>
+        <v>3.992732263664658</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.786967136422594</v>
+        <v>-1.81252128108091</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.494190911233047</v>
+        <v>2.483969253369721</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.295948874493408</v>
+        <v>1.28975861972935</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.986903514811877</v>
+        <v>3.983189361953442</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.785126117364342</v>
+        <v>-1.810680262022659</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.4933613290665</v>
+        <v>2.483139671203173</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.297217101164877</v>
+        <v>1.291026846400818</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.986098461024911</v>
+        <v>3.982384308166475</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.792034822864023</v>
+        <v>-1.81758896752234</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.503671253732547</v>
+        <v>2.49344959586922</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.297217101164877</v>
+        <v>1.291026846400818</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.999171867890829</v>
+        <v>3.995457715032394</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763532</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.793596465678883</v>
+        <v>-1.819150610337199</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.503046596606603</v>
+        <v>2.492824938743276</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.297217101164877</v>
+        <v>1.291026846400818</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.999171867890829</v>
+        <v>3.995457715032394</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.821497252788356</v>
+        <v>-1.847051397446672</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.490410322889816</v>
+        <v>2.480188665026489</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.262620177021942</v>
+        <v>1.256429922257883</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.97693775453207</v>
+        <v>3.973223601673635</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.824530250301029</v>
+        <v>-1.850084394959346</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.485961567861945</v>
+        <v>2.475739909998618</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.259587179509268</v>
+        <v>1.253396924745209</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.971882400001665</v>
+        <v>3.96816824714323</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.844591571577537</v>
+        <v>-1.870145716235853</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.544642998941846</v>
+        <v>2.534421341078519</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.239525858232761</v>
+        <v>1.233335603468702</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.026551566826265</v>
+        <v>4.022837413967829</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.10131238957236</v>
+        <v>-2.126866534230677</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.582266390745763</v>
+        <v>2.572044732882437</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.131111284088946</v>
+        <v>1.124921029324887</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.101814541341823</v>
+        <v>4.098100388483387</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.255298807348501</v>
+        <v>-2.280852952006818</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.589652092780947</v>
+        <v>2.57943043491762</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.131111284088946</v>
+        <v>1.124921029324887</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.170794810487463</v>
+        <v>4.167080657629027</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.204776903520835</v>
+        <v>-2.230331048179152</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.595912056432134</v>
+        <v>2.585690398568807</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.131111284088946</v>
+        <v>1.124921029324887</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.156846012607583</v>
+        <v>4.153131859749148</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.457252057528559</v>
+        <v>-2.482806202186876</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.506792483884458</v>
+        <v>2.496570826021132</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.131111284088946</v>
+        <v>1.124921029324887</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.168716501662997</v>
+        <v>4.165002348804562</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.726724859450267</v>
+        <v>-2.752279004108584</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.400213897634718</v>
+        <v>2.389992239771392</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.131111284088946</v>
+        <v>1.124921029324887</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.169927036181941</v>
+        <v>4.166212883323506</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.884268931179709</v>
+        <v>-2.909823075838025</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.341318011170264</v>
+        <v>2.331096353306937</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.064209478948672</v>
+        <v>1.058019224184613</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.133907695325098</v>
+        <v>4.130193542466662</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.013119481881755</v>
+        <v>-3.038673626540072</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.284855643625634</v>
+        <v>2.274633985762308</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.02321607009795</v>
+        <v>1.017025815333891</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.104389502750855</v>
+        <v>4.100675349892419</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.130087174520646</v>
+        <v>-3.155641319178963</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.400272623269122</v>
+        <v>2.390050965405796</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.02321607009795</v>
+        <v>1.017025815333891</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.266593559449898</v>
+        <v>4.262879406591463</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.231465774675497</v>
+        <v>-3.240359261399917</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.354567821170996</v>
+        <v>2.351010426481228</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.8643296411954772</v>
+        <v>0.931909786405845</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.166108340072229</v>
+        <v>4.20665642719845</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.710463051900209</v>
+        <v>3.71046305190021</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.176388224128809</v>
+        <v>-3.184757384772073</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.386828258958162</v>
+        <v>2.383480594700857</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.8643296411954772</v>
+        <v>0.931909786405845</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.17633775764072</v>
+        <v>4.21688584476694</v>
       </c>
     </row>
   </sheetData>
